--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_14-08-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_14-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D298F3FD-F124-4BE2-985E-D410FEAEF0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11B59D8-6FEA-448C-8388-88FE420779C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4335" yWindow="1980" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="186">
   <si>
     <t>SKU</t>
   </si>
@@ -76,7 +76,7 @@
     <t>25mm EcoTherm Eco-versal Insulation Board</t>
   </si>
   <si>
-    <t>£14.25</t>
+    <t>£15.20</t>
   </si>
   <si>
     <t>£16.92</t>
@@ -148,7 +148,7 @@
     <t>40mm EcoTherm Eco-versal Insulation Board</t>
   </si>
   <si>
-    <t>£21.25</t>
+    <t>£21.40</t>
   </si>
   <si>
     <t>£24.43</t>
@@ -280,7 +280,7 @@
     <t>75mm EcoTherm Eco-versal Insulation Board</t>
   </si>
   <si>
-    <t>£30.00</t>
+    <t>£32.75</t>
   </si>
   <si>
     <t>£35.42</t>
@@ -299,9 +299,6 @@
   </si>
   <si>
     <t>£65.74</t>
-  </si>
-  <si>
-    <t>£32.75</t>
   </si>
   <si>
     <t>£34.38</t>
@@ -1022,7 +1019,7 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -1122,7 +1119,7 @@
         <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J4" t="s">
         <v>22</v>
@@ -1172,7 +1169,7 @@
         <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -1272,7 +1269,7 @@
         <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -1322,7 +1319,7 @@
         <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -1337,413 +1334,413 @@
         <v>92</v>
       </c>
       <c r="N8" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="O8" t="s">
         <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
         <v>95</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>96</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
         <v>97</v>
       </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>98</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>99</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
         <v>100</v>
       </c>
-      <c r="I9" t="s">
-        <v>180</v>
-      </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>101</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>102</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>103</v>
-      </c>
-      <c r="N9" t="s">
-        <v>104</v>
       </c>
       <c r="O9" t="s">
         <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
         <v>106</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>107</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" t="s">
         <v>108</v>
       </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>109</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>110</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>180</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
         <v>111</v>
       </c>
-      <c r="I10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>112</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>113</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>114</v>
-      </c>
-      <c r="N10" t="s">
-        <v>115</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
         <v>117</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
         <v>118</v>
       </c>
-      <c r="C11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>119</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>120</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>181</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
         <v>121</v>
       </c>
-      <c r="I11" t="s">
-        <v>182</v>
-      </c>
-      <c r="J11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>122</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>123</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>124</v>
-      </c>
-      <c r="N11" t="s">
-        <v>125</v>
       </c>
       <c r="O11" t="s">
         <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" t="s">
         <v>127</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
         <v>128</v>
       </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>129</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
         <v>130</v>
       </c>
-      <c r="I12" t="s">
-        <v>183</v>
-      </c>
-      <c r="J12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>131</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>132</v>
-      </c>
-      <c r="N12" t="s">
-        <v>133</v>
       </c>
       <c r="O12" t="s">
         <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" t="s">
         <v>135</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>136</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
         <v>137</v>
       </c>
-      <c r="D13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>138</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>139</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
         <v>140</v>
       </c>
-      <c r="I13" t="s">
-        <v>183</v>
-      </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>141</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>142</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>143</v>
-      </c>
-      <c r="N13" t="s">
-        <v>144</v>
       </c>
       <c r="O13" t="s">
         <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" t="s">
         <v>146</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>147</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
         <v>148</v>
       </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>149</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
         <v>150</v>
       </c>
-      <c r="I14" t="s">
-        <v>184</v>
-      </c>
-      <c r="J14" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>151</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>152</v>
       </c>
-      <c r="M14" t="s">
-        <v>153</v>
-      </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O14" t="s">
         <v>27</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
         <v>155</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>156</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s">
         <v>157</v>
       </c>
-      <c r="D15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>158</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>159</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
         <v>160</v>
       </c>
-      <c r="I15" t="s">
-        <v>185</v>
-      </c>
-      <c r="J15" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>161</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>162</v>
       </c>
-      <c r="M15" t="s">
-        <v>163</v>
-      </c>
       <c r="N15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O15" t="s">
         <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
         <v>164</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>165</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" t="s">
         <v>166</v>
       </c>
-      <c r="D16" t="s">
-        <v>166</v>
-      </c>
-      <c r="E16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>167</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>168</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
+        <v>185</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
         <v>169</v>
       </c>
-      <c r="I16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>170</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>171</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>172</v>
-      </c>
-      <c r="N16" t="s">
-        <v>173</v>
       </c>
       <c r="O16" t="s">
         <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
